--- a/PLTR.xlsx
+++ b/PLTR.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68231855-22FD-4E3F-BD35-F5EF4DB95913}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01A3BD71-B3C6-4E49-8D50-16F521A924FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{6762F9C4-146C-4858-9F14-B8B09877D4A1}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="56">
   <si>
     <t>PLTR</t>
   </si>
@@ -202,6 +202,9 @@
   </si>
   <si>
     <t>Q425</t>
+  </si>
+  <si>
+    <t>FY25</t>
   </si>
 </sst>
 </file>
@@ -669,7 +672,7 @@
         <v>4</v>
       </c>
       <c r="G3" s="2">
-        <v>169.27</v>
+        <v>156.4</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
@@ -680,11 +683,11 @@
         <v>5</v>
       </c>
       <c r="G4" s="3">
-        <f>2284.334012+98.097326+1.005</f>
-        <v>2383.436338</v>
+        <f>2291.470751+99.19996</f>
+        <v>2390.6707109999998</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
@@ -696,7 +699,7 @@
       </c>
       <c r="G5" s="3">
         <f>G3*G4</f>
-        <v>403444.26893326</v>
+        <v>373900.89920039999</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
@@ -704,11 +707,11 @@
         <v>7</v>
       </c>
       <c r="G6" s="3">
-        <f>1615.967+4821.85</f>
-        <v>6437.8170000000009</v>
+        <f>1423.796+5753.247</f>
+        <v>7177.0430000000006</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
@@ -719,7 +722,7 @@
         <v>0</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
@@ -728,7 +731,7 @@
       </c>
       <c r="G8" s="3">
         <f>G5-G6+G7</f>
-        <v>397006.45193326002</v>
+        <v>366723.85620039998</v>
       </c>
     </row>
   </sheetData>
@@ -809,6 +812,9 @@
       <c r="U2" s="4" t="s">
         <v>48</v>
       </c>
+      <c r="V2" s="12" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
@@ -851,7 +857,9 @@
       <c r="U3" s="6">
         <v>1569.605</v>
       </c>
-      <c r="V3" s="6"/>
+      <c r="V3" s="6">
+        <v>2402.2869999999998</v>
+      </c>
       <c r="W3" s="6"/>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.2">
@@ -895,7 +903,9 @@
       <c r="U4" s="6">
         <v>1295.902</v>
       </c>
-      <c r="V4" s="6"/>
+      <c r="V4" s="6">
+        <v>2073.1950000000002</v>
+      </c>
       <c r="W4" s="6"/>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.2">
@@ -941,7 +951,9 @@
       <c r="U5" s="7">
         <v>2865.5070000000001</v>
       </c>
-      <c r="V5" s="7"/>
+      <c r="V5" s="7">
+        <v>4475.4459999999999</v>
+      </c>
       <c r="W5" s="1"/>
       <c r="X5" s="1"/>
       <c r="Y5" s="1"/>
@@ -990,7 +1002,9 @@
       <c r="U6" s="6">
         <v>565.99</v>
       </c>
-      <c r="V6" s="6"/>
+      <c r="V6" s="6">
+        <v>789.17700000000002</v>
+      </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B7" s="2" t="s">
@@ -1066,7 +1080,10 @@
         <f>+U5-U6</f>
         <v>2299.5169999999998</v>
       </c>
-      <c r="V7" s="6"/>
+      <c r="V7" s="6">
+        <f>+V5-V6</f>
+        <v>3686.2689999999998</v>
+      </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B8" s="2" t="s">
@@ -1111,7 +1128,9 @@
       <c r="U8" s="6">
         <v>887.755</v>
       </c>
-      <c r="V8" s="6"/>
+      <c r="V8" s="6">
+        <v>1056.8589999999999</v>
+      </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B9" s="2" t="s">
@@ -1156,7 +1175,9 @@
       <c r="U9" s="6">
         <v>507.87799999999999</v>
       </c>
-      <c r="V9" s="6"/>
+      <c r="V9" s="6">
+        <v>557.67700000000002</v>
+      </c>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B10" s="2" t="s">
@@ -1201,7 +1222,9 @@
       <c r="U10" s="6">
         <v>593.48099999999999</v>
       </c>
-      <c r="V10" s="6"/>
+      <c r="V10" s="6">
+        <v>657.71799999999996</v>
+      </c>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B11" s="2" t="s">
@@ -1251,7 +1274,7 @@
       <c r="N11" s="6"/>
       <c r="O11" s="6"/>
       <c r="P11" s="6">
-        <f t="shared" ref="P11:U11" si="4">P7-SUM(P8:P10)</f>
+        <f t="shared" ref="P11:V11" si="4">P7-SUM(P8:P10)</f>
         <v>0</v>
       </c>
       <c r="Q11" s="6">
@@ -1274,7 +1297,10 @@
         <f t="shared" si="4"/>
         <v>310.40299999999979</v>
       </c>
-      <c r="V11" s="6"/>
+      <c r="V11" s="6">
+        <f t="shared" si="4"/>
+        <v>1414.0149999999999</v>
+      </c>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B12" s="2" t="s">
@@ -1319,7 +1345,9 @@
       <c r="U12" s="6">
         <v>196.792</v>
       </c>
-      <c r="V12" s="6"/>
+      <c r="V12" s="6">
+        <v>229.18100000000001</v>
+      </c>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B13" s="2" t="s">
@@ -1364,7 +1392,9 @@
       <c r="U13" s="6">
         <v>-18.021999999999998</v>
       </c>
-      <c r="V13" s="6"/>
+      <c r="V13" s="6">
+        <v>14.170999999999999</v>
+      </c>
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B14" s="2" t="s">
@@ -1417,7 +1447,7 @@
       <c r="N14" s="6"/>
       <c r="O14" s="6"/>
       <c r="P14" s="6">
-        <f t="shared" ref="P14:U14" si="7">P11+P12+P13</f>
+        <f t="shared" ref="P14:V14" si="7">P11+P12+P13</f>
         <v>0</v>
       </c>
       <c r="Q14" s="6">
@@ -1440,7 +1470,10 @@
         <f t="shared" si="7"/>
         <v>489.17299999999983</v>
       </c>
-      <c r="V14" s="6"/>
+      <c r="V14" s="6">
+        <f t="shared" si="7"/>
+        <v>1657.367</v>
+      </c>
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B15" s="2" t="s">
@@ -1485,7 +1518,9 @@
       <c r="U15" s="6">
         <v>21.254999999999999</v>
       </c>
-      <c r="V15" s="6"/>
+      <c r="V15" s="6">
+        <v>22.724</v>
+      </c>
     </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B16" s="2" t="s">
@@ -1561,7 +1596,10 @@
         <f>+U14-U15</f>
         <v>467.91799999999984</v>
       </c>
-      <c r="V16" s="6"/>
+      <c r="V16" s="6">
+        <f>+V14-V15</f>
+        <v>1634.643</v>
+      </c>
     </row>
     <row r="17" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B17" s="2" t="s">
@@ -1604,7 +1642,9 @@
       <c r="U17" s="6">
         <v>5.7279999999999998</v>
       </c>
-      <c r="V17" s="6"/>
+      <c r="V17" s="6">
+        <v>9.6110000000000007</v>
+      </c>
     </row>
     <row r="18" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B18" s="2" t="s">
@@ -1680,7 +1720,10 @@
         <f>+U16-U17</f>
         <v>462.18999999999983</v>
       </c>
-      <c r="V18" s="6"/>
+      <c r="V18" s="6">
+        <f>+V16-V17</f>
+        <v>1625.0319999999999</v>
+      </c>
     </row>
     <row r="19" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C19" s="6"/>
@@ -1781,7 +1824,10 @@
         <f>+U18/U21</f>
         <v>0.20540289747898255</v>
       </c>
-      <c r="V20" s="6"/>
+      <c r="V20" s="8">
+        <f>+V18/V21</f>
+        <v>0.68577978166889764</v>
+      </c>
     </row>
     <row r="21" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B21" s="2" t="s">
@@ -1826,7 +1872,9 @@
       <c r="U21" s="6">
         <v>2250.163</v>
       </c>
-      <c r="V21" s="6"/>
+      <c r="V21" s="6">
+        <v>2369.6120000000001</v>
+      </c>
     </row>
     <row r="22" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C22" s="6"/>

--- a/PLTR.xlsx
+++ b/PLTR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D0BF66C-6E1A-48BD-BA01-C6E447188816}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E954F593-A0FC-4703-AA5B-3C3E16D1FAD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{6762F9C4-146C-4858-9F14-B8B09877D4A1}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" activeTab="1" xr2:uid="{6762F9C4-146C-4858-9F14-B8B09877D4A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="62">
   <si>
     <t>PLTR</t>
   </si>
@@ -218,6 +218,12 @@
   <si>
     <t>Q426</t>
   </si>
+  <si>
+    <t>CEO</t>
+  </si>
+  <si>
+    <t>Alex Karp</t>
+  </si>
 </sst>
 </file>
 
@@ -228,13 +234,19 @@
     <numFmt numFmtId="165" formatCode="#,##0.0;\(#,##0.0\)"/>
     <numFmt numFmtId="166" formatCode="#,##0.00;\(#,##0.00\)"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -309,33 +321,37 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -672,88 +688,96 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B3A3A29-EDF3-480E-A9BA-5973530E4A9A}">
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.42578125" style="2" customWidth="1"/>
     <col min="2" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="F3" s="2" t="s">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="H3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="2">
-        <v>133.06</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I3" s="2">
+        <v>160.4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B4" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="14">
-        <f>2296.071334+100.235643+1.005</f>
-        <v>2397.3119770000003</v>
-      </c>
-      <c r="H4" s="13" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I4" s="14">
+        <f>2300.717329+101.340151+1.005</f>
+        <v>2403.0624800000001</v>
+      </c>
+      <c r="J4" s="16" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B5" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="H5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="14">
-        <f>+G3*G4</f>
-        <v>318986.33165962005</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="F6" s="2" t="s">
+      <c r="I5" s="14">
+        <f>+I3*I4</f>
+        <v>385451.221792</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="H6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G6" s="3">
-        <f>2291.631+5734.782</f>
-        <v>8026.4130000000005</v>
-      </c>
-      <c r="H6" s="13" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="F7" s="2" t="s">
+      <c r="I6" s="3">
+        <f>2030.047+7379.052</f>
+        <v>9409.0990000000002</v>
+      </c>
+      <c r="J6" s="16" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="H7" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="G7" s="14">
+      <c r="I7" s="14">
         <v>0</v>
       </c>
-      <c r="H7" s="13" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="F8" s="2" t="s">
+      <c r="J7" s="16" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="H8" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="G8" s="3">
-        <f>G5-G6+G7</f>
-        <v>310959.91865962005</v>
+      <c r="I8" s="3">
+        <f>I5-I6+I7</f>
+        <v>376042.12279200001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="H10" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="I10" s="15" t="s">
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -883,7 +907,9 @@
       <c r="O3" s="6">
         <v>858.41</v>
       </c>
-      <c r="P3" s="6"/>
+      <c r="P3" s="6">
+        <v>990.03200000000004</v>
+      </c>
       <c r="Q3" s="6"/>
       <c r="R3" s="6"/>
       <c r="S3" s="6"/>
@@ -935,7 +961,9 @@
       <c r="O4" s="6">
         <v>774.173</v>
       </c>
-      <c r="P4" s="6"/>
+      <c r="P4" s="6">
+        <v>945.43200000000002</v>
+      </c>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
       <c r="S4" s="6"/>
@@ -987,7 +1015,9 @@
       <c r="O5" s="7">
         <v>1632.5830000000001</v>
       </c>
-      <c r="P5" s="7"/>
+      <c r="P5" s="7">
+        <v>1935.4639999999999</v>
+      </c>
       <c r="Q5" s="7"/>
       <c r="R5" s="7"/>
       <c r="S5" s="7"/>
@@ -1044,7 +1074,9 @@
       <c r="O6" s="6">
         <v>215.798</v>
       </c>
-      <c r="P6" s="6"/>
+      <c r="P6" s="6">
+        <v>296.87</v>
+      </c>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
       <c r="S6" s="6"/>
@@ -1113,14 +1145,17 @@
         <v>973.78500000000008</v>
       </c>
       <c r="N7" s="6">
-        <f t="shared" ref="N7:O7" si="1">+N5-N6</f>
+        <f t="shared" ref="N7:P7" si="1">+N5-N6</f>
         <v>0</v>
       </c>
       <c r="O7" s="6">
         <f t="shared" si="1"/>
         <v>1416.7850000000001</v>
       </c>
-      <c r="P7" s="6"/>
+      <c r="P7" s="6">
+        <f t="shared" si="1"/>
+        <v>1638.5940000000001</v>
+      </c>
       <c r="Q7" s="6"/>
       <c r="R7" s="6"/>
       <c r="S7" s="6"/>
@@ -1186,7 +1221,9 @@
       <c r="O8" s="6">
         <v>319.22000000000003</v>
       </c>
-      <c r="P8" s="6"/>
+      <c r="P8" s="6">
+        <v>339.5</v>
+      </c>
       <c r="Q8" s="6"/>
       <c r="R8" s="6"/>
       <c r="S8" s="6"/>
@@ -1239,7 +1276,9 @@
       <c r="O9" s="6">
         <v>160.98099999999999</v>
       </c>
-      <c r="P9" s="6"/>
+      <c r="P9" s="6">
+        <v>192.51300000000001</v>
+      </c>
       <c r="Q9" s="6"/>
       <c r="R9" s="6"/>
       <c r="S9" s="6"/>
@@ -1292,7 +1331,9 @@
       <c r="O10" s="6">
         <v>182.58600000000001</v>
       </c>
-      <c r="P10" s="6"/>
+      <c r="P10" s="6">
+        <v>194.577</v>
+      </c>
       <c r="Q10" s="6"/>
       <c r="R10" s="6"/>
       <c r="S10" s="6"/>
@@ -1367,7 +1408,7 @@
       </c>
       <c r="P11" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>912.00400000000002</v>
       </c>
       <c r="Q11" s="6"/>
       <c r="R11" s="6"/>
@@ -1434,7 +1475,9 @@
       <c r="O12" s="6">
         <v>66.394000000000005</v>
       </c>
-      <c r="P12" s="6"/>
+      <c r="P12" s="6">
+        <v>77.504999999999995</v>
+      </c>
       <c r="Q12" s="6"/>
       <c r="R12" s="6"/>
       <c r="S12" s="6"/>
@@ -1487,7 +1530,9 @@
       <c r="O13" s="6">
         <v>68.209000000000003</v>
       </c>
-      <c r="P13" s="6"/>
+      <c r="P13" s="6">
+        <v>91.835999999999999</v>
+      </c>
       <c r="Q13" s="6"/>
       <c r="R13" s="6"/>
       <c r="S13" s="6"/>
@@ -1565,7 +1610,7 @@
       </c>
       <c r="P14" s="6">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1081.345</v>
       </c>
       <c r="Q14" s="6"/>
       <c r="R14" s="6"/>
@@ -1632,7 +1677,9 @@
       <c r="O15" s="6">
         <v>12.199</v>
       </c>
-      <c r="P15" s="6"/>
+      <c r="P15" s="6">
+        <v>15.382999999999999</v>
+      </c>
       <c r="Q15" s="6"/>
       <c r="R15" s="6"/>
       <c r="S15" s="6"/>
@@ -1710,7 +1757,7 @@
       </c>
       <c r="P16" s="6">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1065.962</v>
       </c>
       <c r="Q16" s="6"/>
       <c r="R16" s="6"/>
@@ -1775,7 +1822,9 @@
       <c r="O17" s="6">
         <v>5.875</v>
       </c>
-      <c r="P17" s="6"/>
+      <c r="P17" s="6">
+        <v>4.0720000000000001</v>
+      </c>
       <c r="Q17" s="6"/>
       <c r="R17" s="6"/>
       <c r="S17" s="6"/>
@@ -1853,7 +1902,7 @@
       </c>
       <c r="P18" s="6">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>1061.8900000000001</v>
       </c>
       <c r="Q18" s="6"/>
       <c r="R18" s="6"/>
@@ -1969,9 +2018,9 @@
         <f t="shared" si="16"/>
         <v>0.36610273995778386</v>
       </c>
-      <c r="P20" s="8" t="e">
+      <c r="P20" s="8">
         <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+        <v>0.4441841471443691</v>
       </c>
       <c r="Q20" s="8"/>
       <c r="R20" s="8"/>
@@ -2038,7 +2087,9 @@
       <c r="O21" s="6">
         <v>2393.8690000000001</v>
       </c>
-      <c r="P21" s="6"/>
+      <c r="P21" s="6">
+        <v>2399.8200000000002</v>
+      </c>
       <c r="Q21" s="6"/>
       <c r="R21" s="6"/>
       <c r="S21" s="6"/>
@@ -2128,8 +2179,14 @@
         <f t="shared" si="25"/>
         <v>0.76278279869312438</v>
       </c>
-      <c r="P23" s="9"/>
-      <c r="Q23" s="9"/>
+      <c r="P23" s="9">
+        <f t="shared" ref="P23:P25" si="26">P3/L3-1</f>
+        <v>0.79034798538110596</v>
+      </c>
+      <c r="Q23" s="9">
+        <f t="shared" ref="Q23:Q25" si="27">Q3/M3-1</f>
+        <v>-1</v>
+      </c>
       <c r="R23" s="9"/>
       <c r="S23" s="6"/>
       <c r="T23" s="6"/>
@@ -2184,8 +2241,14 @@
         <f t="shared" si="25"/>
         <v>0.95058857321387191</v>
       </c>
-      <c r="P24" s="9"/>
-      <c r="Q24" s="9"/>
+      <c r="P24" s="9">
+        <f t="shared" si="26"/>
+        <v>1.0976317576112566</v>
+      </c>
+      <c r="Q24" s="9">
+        <f t="shared" si="27"/>
+        <v>-1</v>
+      </c>
       <c r="R24" s="9"/>
       <c r="S24" s="6"/>
       <c r="T24" s="6"/>
@@ -2205,7 +2268,7 @@
       <c r="E25" s="7"/>
       <c r="F25" s="7"/>
       <c r="G25" s="11" t="e">
-        <f t="shared" ref="G25" si="26">G5/C5-1</f>
+        <f t="shared" ref="G25" si="28">G5/C5-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="H25" s="11">
@@ -2213,11 +2276,11 @@
         <v>0.2715401909183468</v>
       </c>
       <c r="I25" s="11" t="e">
-        <f t="shared" ref="I25:J25" si="27">I5/E5-1</f>
+        <f t="shared" ref="I25:J25" si="29">I5/E5-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="J25" s="11" t="e">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K25" s="11">
@@ -2240,8 +2303,14 @@
         <f t="shared" si="25"/>
         <v>0.8471163256416494</v>
       </c>
-      <c r="P25" s="11"/>
-      <c r="Q25" s="11"/>
+      <c r="P25" s="11">
+        <f t="shared" si="26"/>
+        <v>0.92833494570572594</v>
+      </c>
+      <c r="Q25" s="11">
+        <f t="shared" si="27"/>
+        <v>-1</v>
+      </c>
       <c r="R25" s="11"/>
       <c r="S25" s="6"/>
       <c r="T25" s="6"/>
@@ -2257,59 +2326,65 @@
         <v>33</v>
       </c>
       <c r="C26" s="9" t="e">
-        <f t="shared" ref="C26:H26" si="28">C7/C5</f>
+        <f t="shared" ref="C26:H26" si="30">C7/C5</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D26" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0.79955823647099189</v>
       </c>
       <c r="E26" s="9" t="e">
-        <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F26" s="9" t="e">
-        <f t="shared" si="28"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G26" s="9">
-        <f t="shared" si="28"/>
-        <v>0.81674306575786437</v>
-      </c>
-      <c r="H26" s="9">
-        <f t="shared" si="28"/>
-        <v>0.81041799998230435</v>
-      </c>
-      <c r="I26" s="9">
-        <f t="shared" ref="I26:J26" si="29">I7/I5</f>
-        <v>0.79788316177727303</v>
-      </c>
-      <c r="J26" s="9" t="e">
-        <f t="shared" si="29"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K26" s="9">
-        <f t="shared" ref="K26:N26" si="30">K7/K5</f>
-        <v>0.8043004791509919</v>
-      </c>
-      <c r="L26" s="9">
-        <f t="shared" si="30"/>
-        <v>0.80777664972596319</v>
-      </c>
-      <c r="M26" s="9">
-        <f t="shared" si="30"/>
-        <v>0.82447853342499988</v>
-      </c>
-      <c r="N26" s="9" t="e">
         <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="F26" s="9" t="e">
+        <f t="shared" si="30"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G26" s="9">
+        <f t="shared" si="30"/>
+        <v>0.81674306575786437</v>
+      </c>
+      <c r="H26" s="9">
+        <f t="shared" si="30"/>
+        <v>0.81041799998230435</v>
+      </c>
+      <c r="I26" s="9">
+        <f t="shared" ref="I26:J26" si="31">I7/I5</f>
+        <v>0.79788316177727303</v>
+      </c>
+      <c r="J26" s="9" t="e">
+        <f t="shared" si="31"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K26" s="9">
+        <f t="shared" ref="K26:N26" si="32">K7/K5</f>
+        <v>0.8043004791509919</v>
+      </c>
+      <c r="L26" s="9">
+        <f t="shared" si="32"/>
+        <v>0.80777664972596319</v>
+      </c>
+      <c r="M26" s="9">
+        <f t="shared" si="32"/>
+        <v>0.82447853342499988</v>
+      </c>
+      <c r="N26" s="9" t="e">
+        <f t="shared" si="32"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="O26" s="9">
-        <f t="shared" ref="O26" si="31">O7/O5</f>
+        <f t="shared" ref="O26:Q26" si="33">O7/O5</f>
         <v>0.86781805274218826</v>
       </c>
-      <c r="P26" s="9"/>
-      <c r="Q26" s="9"/>
+      <c r="P26" s="9">
+        <f t="shared" si="33"/>
+        <v>0.84661559192007707</v>
+      </c>
+      <c r="Q26" s="9" t="e">
+        <f t="shared" si="33"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="R26" s="9"/>
       <c r="S26" s="6"/>
       <c r="T26" s="6"/>
@@ -2325,59 +2400,65 @@
         <v>34</v>
       </c>
       <c r="C27" s="9" t="e">
-        <f t="shared" ref="C27:H27" si="32">C11/C5</f>
+        <f t="shared" ref="C27:H27" si="34">C11/C5</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D27" s="9">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>1.8889328485684791E-2</v>
       </c>
       <c r="E27" s="9" t="e">
-        <f t="shared" si="32"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F27" s="9" t="e">
-        <f t="shared" si="32"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G27" s="9">
-        <f t="shared" si="32"/>
-        <v>0.12757334628019451</v>
-      </c>
-      <c r="H27" s="9">
-        <f t="shared" si="32"/>
-        <v>0.1553365559019308</v>
-      </c>
-      <c r="I27" s="9">
-        <f t="shared" ref="I27:J27" si="33">I11/I5</f>
-        <v>0.15594418317445788</v>
-      </c>
-      <c r="J27" s="9" t="e">
-        <f t="shared" si="33"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K27" s="9">
-        <f t="shared" ref="K27:N27" si="34">K11/K5</f>
-        <v>0.19918199252139773</v>
-      </c>
-      <c r="L27" s="9">
-        <f t="shared" si="34"/>
-        <v>0.26832500246588364</v>
-      </c>
-      <c r="M27" s="9">
-        <f t="shared" si="34"/>
-        <v>0.33295966783281916</v>
-      </c>
-      <c r="N27" s="9" t="e">
         <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="F27" s="9" t="e">
+        <f t="shared" si="34"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G27" s="9">
+        <f t="shared" si="34"/>
+        <v>0.12757334628019451</v>
+      </c>
+      <c r="H27" s="9">
+        <f t="shared" si="34"/>
+        <v>0.1553365559019308</v>
+      </c>
+      <c r="I27" s="9">
+        <f t="shared" ref="I27:J27" si="35">I11/I5</f>
+        <v>0.15594418317445788</v>
+      </c>
+      <c r="J27" s="9" t="e">
+        <f t="shared" si="35"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K27" s="9">
+        <f t="shared" ref="K27:N27" si="36">K11/K5</f>
+        <v>0.19918199252139773</v>
+      </c>
+      <c r="L27" s="9">
+        <f t="shared" si="36"/>
+        <v>0.26832500246588364</v>
+      </c>
+      <c r="M27" s="9">
+        <f t="shared" si="36"/>
+        <v>0.33295966783281916</v>
+      </c>
+      <c r="N27" s="9" t="e">
+        <f t="shared" si="36"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="O27" s="9">
-        <f t="shared" ref="O27" si="35">O11/O5</f>
+        <f t="shared" ref="O27:Q27" si="37">O11/O5</f>
         <v>0.46184359386322166</v>
       </c>
-      <c r="P27" s="9"/>
-      <c r="Q27" s="9"/>
+      <c r="P27" s="9">
+        <f t="shared" si="37"/>
+        <v>0.47120690439088508</v>
+      </c>
+      <c r="Q27" s="9" t="e">
+        <f t="shared" si="37"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="R27" s="9"/>
       <c r="S27" s="6"/>
       <c r="T27" s="6"/>
@@ -2393,59 +2474,65 @@
         <v>35</v>
       </c>
       <c r="C28" s="9" t="e">
-        <f t="shared" ref="C28:H28" si="36">C15/C14</f>
+        <f t="shared" ref="C28:H28" si="38">C15/C14</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D28" s="9">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>7.226308957161412E-2</v>
       </c>
       <c r="E28" s="9" t="e">
-        <f t="shared" si="36"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F28" s="9" t="e">
-        <f t="shared" si="36"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G28" s="9">
-        <f t="shared" si="36"/>
-        <v>4.20217375604824E-2</v>
-      </c>
-      <c r="H28" s="9">
-        <f t="shared" si="36"/>
-        <v>3.6864427851860282E-2</v>
-      </c>
-      <c r="I28" s="9">
-        <f t="shared" ref="I28:J28" si="37">I15/I14</f>
-        <v>4.9691377664651613E-2</v>
-      </c>
-      <c r="J28" s="9" t="e">
-        <f t="shared" si="37"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K28" s="9">
-        <f t="shared" ref="K28:N28" si="38">K15/K14</f>
-        <v>2.5072095147683104E-2</v>
-      </c>
-      <c r="L28" s="9">
-        <f t="shared" si="38"/>
-        <v>1.0825847161677223E-2</v>
-      </c>
-      <c r="M28" s="9">
-        <f t="shared" si="38"/>
-        <v>7.8105976886624576E-3</v>
-      </c>
-      <c r="N28" s="9" t="e">
         <f t="shared" si="38"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="F28" s="9" t="e">
+        <f t="shared" si="38"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G28" s="9">
+        <f t="shared" si="38"/>
+        <v>4.20217375604824E-2</v>
+      </c>
+      <c r="H28" s="9">
+        <f t="shared" si="38"/>
+        <v>3.6864427851860282E-2</v>
+      </c>
+      <c r="I28" s="9">
+        <f t="shared" ref="I28:J28" si="39">I15/I14</f>
+        <v>4.9691377664651613E-2</v>
+      </c>
+      <c r="J28" s="9" t="e">
+        <f t="shared" si="39"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K28" s="9">
+        <f t="shared" ref="K28:N28" si="40">K15/K14</f>
+        <v>2.5072095147683104E-2</v>
+      </c>
+      <c r="L28" s="9">
+        <f t="shared" si="40"/>
+        <v>1.0825847161677223E-2</v>
+      </c>
+      <c r="M28" s="9">
+        <f t="shared" si="40"/>
+        <v>7.8105976886624576E-3</v>
+      </c>
+      <c r="N28" s="9" t="e">
+        <f t="shared" si="40"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="O28" s="9">
-        <f t="shared" ref="O28" si="39">O15/O14</f>
+        <f t="shared" ref="O28:Q28" si="41">O15/O14</f>
         <v>1.3728321260048096E-2</v>
       </c>
-      <c r="P28" s="9"/>
-      <c r="Q28" s="9"/>
+      <c r="P28" s="9">
+        <f t="shared" si="41"/>
+        <v>1.4225802126055976E-2</v>
+      </c>
+      <c r="Q28" s="9" t="e">
+        <f t="shared" si="41"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="R28" s="9"/>
       <c r="S28" s="6"/>
       <c r="T28" s="6"/>
